--- a/main/ig/StructureDefinition-fr-lm-specimen.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-specimen.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1251" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="142">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T15:39:37+00:00</t>
+    <t>2026-08-05T12:15:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -108,7 +108,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-entry|0.1.0</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Base|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -250,361 +250,189 @@
     <t>Base</t>
   </si>
   <si>
-    <t>fr-lm-specimen.header</t>
+    <t>fr-lm-specimen.identifier</t>
   </si>
   <si>
     <t>1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier
+</t>
+  </si>
+  <si>
+    <t>Identifiant unique de l'échantillon, au sein d'un périmètre défini. Exemple : identifiant attribué par le système du préleveur, identifiant attribué par le laboratoire, etc. Plusieurs identifiants peuvent être utilisés.</t>
+  </si>
+  <si>
+    <t>fr-lm-specimen.status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Disponibilité du prélèvement</t>
+  </si>
+  <si>
+    <t>(preferred): HL7 specimen-status</t>
+  </si>
+  <si>
+    <t>fr-lm-specimen.type</t>
+  </si>
+  <si>
+    <t>Échantillon prélevé</t>
+  </si>
+  <si>
+    <t>jdv-specimen-type-cisis (1.2.250.1.213.1.1.5.819)</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-specimen-type-cisis|20260619134042</t>
+  </si>
+  <si>
+    <t>fr-lm-specimen.specimenSource[x]</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-patient
+https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-locationhttps://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-device</t>
+  </si>
+  <si>
+    <t>Origine du prélèvement : il peut provenir d'un patient, d'un lieu ou d'un dispositif</t>
+  </si>
+  <si>
+    <t>fr-lm-specimen.parentSpecimen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-specimen
+</t>
+  </si>
+  <si>
+    <t>Prélèvement dont provient cet échantillon</t>
+  </si>
+  <si>
+    <t>fr-lm-specimen.request</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-service-request
+</t>
+  </si>
+  <si>
+    <t>Demande à l'origine du prélèvement</t>
+  </si>
+  <si>
+    <t>fr-lm-specimen.combined</t>
+  </si>
+  <si>
+    <t>Binding Description: (preferred): HL7 specimen-combined</t>
+  </si>
+  <si>
+    <t>(preferred): HL7 specimen-combined</t>
+  </si>
+  <si>
+    <t>fr-lm-specimen.collection</t>
   </si>
   <si>
     <t xml:space="preserve">Base
 </t>
   </si>
   <si>
-    <t>Métadonnées de base</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header</t>
-  </si>
-  <si>
-    <t>fr-lm-specimen.header.subject</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-patient
+    <t>Détails de la collecte</t>
+  </si>
+  <si>
+    <t>fr-lm-specimen.collection.performer[x]</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-health-professional
+https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-organisationhttps://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-patienthttps://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-related-person</t>
+  </si>
+  <si>
+    <t>Organisation prélevante</t>
+  </si>
+  <si>
+    <t>fr-lm-specimen.collection.collected[x]</t>
+  </si>
+  <si>
+    <t>dateTime
+Period</t>
+  </si>
+  <si>
+    <t>Date du prélèvement</t>
+  </si>
+  <si>
+    <t>fr-lm-specimen.collection.quantity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity
 </t>
   </si>
   <si>
-    <t>Patient / Usager</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.subject</t>
-  </si>
-  <si>
-    <t>fr-lm-specimen.header.identifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier
+    <t>Quantité</t>
+  </si>
+  <si>
+    <t>fr-lm-specimen.collection.method</t>
+  </si>
+  <si>
+    <t>Acte de prélèvement</t>
+  </si>
+  <si>
+    <t>NABM (1.2.250.1.215.300.2) ou 33882-2 [LOINC] Prélèvement</t>
+  </si>
+  <si>
+    <t>fr-lm-specimen.collection.device</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-device-use
 </t>
   </si>
   <si>
-    <t>Identifiant de l’entrée</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.identifier</t>
-  </si>
-  <si>
-    <t>fr-lm-specimen.header.author[x]</t>
-  </si>
-  <si>
-    <t>author[x] peut correspondre soit à un professionnel, soit à une organisation, soit à un système.</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.author[x]</t>
-  </si>
-  <si>
-    <t>fr-lm-specimen.header.author[x].authorProfessional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-health-professional
+    <t>Dispositif utilisé</t>
+  </si>
+  <si>
+    <t>fr-lm-specimen.collection.additive[x]</t>
+  </si>
+  <si>
+    <t>CodeableConcept
+https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-device</t>
+  </si>
+  <si>
+    <t>Produit utilisé</t>
+  </si>
+  <si>
+    <t>fr-lm-specimen.collection.bodySite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-body-structure
 </t>
   </si>
   <si>
-    <t>L'auteur est un professionnel de santé</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.author[x].authorProfessional</t>
-  </si>
-  <si>
-    <t>fr-lm-specimen.header.author[x].authorOrganisation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-organisation
+    <t>Localisation du prélèvement</t>
+  </si>
+  <si>
+    <t>fr-lm-specimen.receivedDate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
 </t>
   </si>
   <si>
-    <t>L'auteur est une organisation</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.author[x].authorOrganisation</t>
-  </si>
-  <si>
-    <t>fr-lm-specimen.header.author[x].authorDevice</t>
+    <t>Date de réception de l'échantillon</t>
+  </si>
+  <si>
+    <t>fr-lm-specimen.container</t>
+  </si>
+  <si>
+    <t>Contenant du prélèvement</t>
+  </si>
+  <si>
+    <t>fr-lm-specimen.container.specimenQuantity</t>
+  </si>
+  <si>
+    <t>Quantité de prélèvement dans le contenant</t>
+  </si>
+  <si>
+    <t>fr-lm-specimen.container.containerDevice</t>
   </si>
   <si>
     <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-device
 </t>
-  </si>
-  <si>
-    <t>L'auteur est un système</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.author[x].authorDevice</t>
-  </si>
-  <si>
-    <t>fr-lm-specimen.header.performer[x]</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-health-professional
-https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-organisation</t>
-  </si>
-  <si>
-    <t>Exécutant (performer)</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.performer[x]</t>
-  </si>
-  <si>
-    <t>fr-lm-specimen.header.participant[x]</t>
-  </si>
-  <si>
-    <t>Participant</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.participant[x]</t>
-  </si>
-  <si>
-    <t>fr-lm-specimen.header.participant[x].participantProfessional</t>
-  </si>
-  <si>
-    <t>Le participant est un professionnel de santé</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.participant[x].participantProfessional</t>
-  </si>
-  <si>
-    <t>fr-lm-specimen.header.participant[x].participantOrganisation</t>
-  </si>
-  <si>
-    <t>Le participant est une organisation</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.participant[x].participantOrganisation</t>
-  </si>
-  <si>
-    <t>fr-lm-specimen.header.participant[x].participantDevice</t>
-  </si>
-  <si>
-    <t>Le participant est un système</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.participant[x].participantDevice</t>
-  </si>
-  <si>
-    <t>fr-lm-specimen.header.informant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-informant
-</t>
-  </si>
-  <si>
-    <t>Informateur</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.informant</t>
-  </si>
-  <si>
-    <t>fr-lm-specimen.header.date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
-</t>
-  </si>
-  <si>
-    <t>Date/Heure de création par l'auteur</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.date</t>
-  </si>
-  <si>
-    <t>fr-lm-specimen.header.status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>Disponibilité du prélèvement</t>
-  </si>
-  <si>
-    <t>Statut</t>
-  </si>
-  <si>
-    <t>(preferred): HL7 specimen-status</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.status</t>
-  </si>
-  <si>
-    <t>fr-lm-specimen.header.source</t>
-  </si>
-  <si>
-    <t>Source</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.source</t>
-  </si>
-  <si>
-    <t>fr-lm-specimen.header.language</t>
-  </si>
-  <si>
-    <t>'fr-FR' pour français métropolitain (la casse des caractères doit être respectée)
-La partie en minuscules indique le code de la langue utilisée (ISO-639-1)
-La partie en majuscules indique le code pays (ISO-3166)</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.language</t>
-  </si>
-  <si>
-    <t>fr-lm-specimen.identifier</t>
-  </si>
-  <si>
-    <t>Identifiant unique de l'échantillon, au sein d'un périmètre défini. Exemple : identifiant attribué par le système du préleveur, identifiant attribué par le laboratoire, etc. Plusieurs identifiants peuvent être utilisés.</t>
-  </si>
-  <si>
-    <t>fr-lm-specimen.type</t>
-  </si>
-  <si>
-    <t>Échantillon prélevé</t>
-  </si>
-  <si>
-    <t>jdv-specimen-type-cisis (1.2.250.1.213.1.1.5.819)</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-specimen-type-cisis|20260619134042</t>
-  </si>
-  <si>
-    <t>fr-lm-specimen.specimenSource[x]</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-patient
-https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-locationhttps://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-device</t>
-  </si>
-  <si>
-    <t>Origine du prélèvement : il peut provenir d'un patient, d'un lieu ou d'un dispositif</t>
-  </si>
-  <si>
-    <t>fr-lm-specimen.parentSpecimen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-specimen
-</t>
-  </si>
-  <si>
-    <t>Prélèvement dont provient cet échantillon</t>
-  </si>
-  <si>
-    <t>fr-lm-specimen.request</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-service-request
-</t>
-  </si>
-  <si>
-    <t>Demande à l'origine du prélèvement</t>
-  </si>
-  <si>
-    <t>fr-lm-specimen.combined</t>
-  </si>
-  <si>
-    <t>Binding Description: (preferred): HL7 specimen-combined</t>
-  </si>
-  <si>
-    <t>(preferred): HL7 specimen-combined</t>
-  </si>
-  <si>
-    <t>fr-lm-specimen.collection</t>
-  </si>
-  <si>
-    <t>Détails de la collecte</t>
-  </si>
-  <si>
-    <t>fr-lm-specimen.collection.performer[x]</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-health-professional
-https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-organisationhttps://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-patienthttps://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-related-person</t>
-  </si>
-  <si>
-    <t>Organisation prélevante</t>
-  </si>
-  <si>
-    <t>fr-lm-specimen.collection.collected[x]</t>
-  </si>
-  <si>
-    <t>dateTime
-Period</t>
-  </si>
-  <si>
-    <t>Date du prélèvement</t>
-  </si>
-  <si>
-    <t>fr-lm-specimen.collection.quantity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantity
-</t>
-  </si>
-  <si>
-    <t>Quantité</t>
-  </si>
-  <si>
-    <t>fr-lm-specimen.collection.method</t>
-  </si>
-  <si>
-    <t>Acte de prélèvement</t>
-  </si>
-  <si>
-    <t>NABM (1.2.250.1.215.300.2) ou 33882-2 [LOINC] Prélèvement</t>
-  </si>
-  <si>
-    <t>fr-lm-specimen.collection.device</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-device-use
-</t>
-  </si>
-  <si>
-    <t>Dispositif utilisé</t>
-  </si>
-  <si>
-    <t>fr-lm-specimen.collection.additive[x]</t>
-  </si>
-  <si>
-    <t>CodeableConcept
-https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-device</t>
-  </si>
-  <si>
-    <t>Produit utilisé</t>
-  </si>
-  <si>
-    <t>fr-lm-specimen.collection.bodySite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-body-structure
-</t>
-  </si>
-  <si>
-    <t>Localisation du prélèvement</t>
-  </si>
-  <si>
-    <t>fr-lm-specimen.receivedDate</t>
-  </si>
-  <si>
-    <t>Date de réception de l'échantillon</t>
-  </si>
-  <si>
-    <t>fr-lm-specimen.container</t>
-  </si>
-  <si>
-    <t>Contenant du prélèvement</t>
-  </si>
-  <si>
-    <t>fr-lm-specimen.container.specimenQuantity</t>
-  </si>
-  <si>
-    <t>Quantité de prélèvement dans le contenant</t>
-  </si>
-  <si>
-    <t>fr-lm-specimen.container.containerDevice</t>
   </si>
   <si>
     <t>Dispositif utilisé comme contenant</t>
@@ -928,11 +756,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ39"/>
+  <dimension ref="A1:AJ23"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="49.10546875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="49.10546875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="35.59375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="35.59375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -962,7 +790,7 @@
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="45.68359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="35.59375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -1194,7 +1022,7 @@
         <v>79</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>73</v>
@@ -1263,13 +1091,13 @@
         <v>73</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>73</v>
@@ -1280,10 +1108,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1291,7 +1119,7 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G4" t="s" s="2">
         <v>79</v>
@@ -1306,13 +1134,13 @@
         <v>73</v>
       </c>
       <c r="K4" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="L4" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="M4" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1342,7 +1170,7 @@
         <v>73</v>
       </c>
       <c r="Y4" t="s" s="2">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="Z4" t="s" s="2">
         <v>73</v>
@@ -1363,10 +1191,10 @@
         <v>73</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH4" t="s" s="2">
         <v>79</v>
@@ -1380,10 +1208,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1394,7 +1222,7 @@
         <v>74</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>73</v>
@@ -1406,13 +1234,13 @@
         <v>73</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1442,10 +1270,10 @@
         <v>73</v>
       </c>
       <c r="Y5" t="s" s="2">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="Z5" t="s" s="2">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="AA5" t="s" s="2">
         <v>73</v>
@@ -1463,13 +1291,13 @@
         <v>73</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>73</v>
@@ -1480,10 +1308,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1494,7 +1322,7 @@
         <v>74</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>73</v>
@@ -1506,7 +1334,7 @@
         <v>73</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="L6" t="s" s="2">
         <v>92</v>
@@ -1563,13 +1391,13 @@
         <v>73</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>73</v>
@@ -1580,10 +1408,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1606,13 +1434,13 @@
         <v>73</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="L7" t="s" s="2">
-        <v>96</v>
-      </c>
       <c r="M7" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1663,7 +1491,7 @@
         <v>73</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>74</v>
@@ -1680,10 +1508,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1706,13 +1534,13 @@
         <v>73</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1763,7 +1591,7 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>74</v>
@@ -1780,10 +1608,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1794,7 +1622,7 @@
         <v>74</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>73</v>
@@ -1806,13 +1634,13 @@
         <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1842,7 +1670,7 @@
         <v>73</v>
       </c>
       <c r="Y9" t="s" s="2">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="Z9" t="s" s="2">
         <v>73</v>
@@ -1863,13 +1691,13 @@
         <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>73</v>
@@ -1880,10 +1708,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1906,13 +1734,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1963,7 +1791,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -1980,10 +1808,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1994,7 +1822,7 @@
         <v>74</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>73</v>
@@ -2006,13 +1834,13 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2063,13 +1891,13 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>73</v>
@@ -2080,10 +1908,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2091,10 +1919,10 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>73</v>
@@ -2106,13 +1934,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2163,13 +1991,13 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>73</v>
@@ -2180,10 +2008,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2194,7 +2022,7 @@
         <v>74</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>73</v>
@@ -2206,13 +2034,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2263,13 +2091,13 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>73</v>
@@ -2280,10 +2108,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2294,7 +2122,7 @@
         <v>74</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>73</v>
@@ -2306,13 +2134,13 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2342,7 +2170,7 @@
         <v>73</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>73</v>
+        <v>116</v>
       </c>
       <c r="Z14" t="s" s="2">
         <v>73</v>
@@ -2363,13 +2191,13 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>73</v>
@@ -2380,10 +2208,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2406,13 +2234,13 @@
         <v>73</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2463,7 +2291,7 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
@@ -2480,10 +2308,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2494,7 +2322,7 @@
         <v>74</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>73</v>
@@ -2506,13 +2334,13 @@
         <v>73</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2563,13 +2391,13 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>73</v>
@@ -2580,10 +2408,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2606,13 +2434,13 @@
         <v>73</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2642,7 +2470,7 @@
         <v>73</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>134</v>
+        <v>73</v>
       </c>
       <c r="Z17" t="s" s="2">
         <v>73</v>
@@ -2663,7 +2491,7 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>74</v>
@@ -2680,10 +2508,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2691,7 +2519,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>79</v>
@@ -2706,13 +2534,13 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2763,10 +2591,10 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>79</v>
@@ -2780,10 +2608,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2794,7 +2622,7 @@
         <v>74</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>73</v>
@@ -2806,13 +2634,13 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2863,13 +2691,13 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>73</v>
@@ -2880,10 +2708,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2891,10 +2719,10 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>73</v>
@@ -2906,13 +2734,13 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2963,13 +2791,13 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>73</v>
@@ -2980,10 +2808,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2991,7 +2819,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>79</v>
@@ -3006,13 +2834,13 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3042,10 +2870,10 @@
         <v>73</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>146</v>
+        <v>73</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>147</v>
+        <v>73</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>73</v>
@@ -3063,10 +2891,10 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>79</v>
@@ -3080,10 +2908,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3094,7 +2922,7 @@
         <v>74</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>73</v>
@@ -3106,13 +2934,13 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>149</v>
+        <v>83</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3142,7 +2970,7 @@
         <v>73</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>73</v>
+        <v>138</v>
       </c>
       <c r="Z22" t="s" s="2">
         <v>73</v>
@@ -3163,13 +2991,13 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>73</v>
@@ -3180,10 +3008,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3194,7 +3022,7 @@
         <v>74</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>73</v>
@@ -3206,13 +3034,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3263,1618 +3091,18 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="C24" s="2"/>
-      <c r="D24" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E24" s="2"/>
-      <c r="F24" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G24" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H24" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I24" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J24" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K24" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="L24" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
-      <c r="P24" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q24" s="2"/>
-      <c r="R24" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S24" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T24" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U24" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V24" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W24" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X24" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y24" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z24" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA24" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB24" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC24" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD24" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE24" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF24" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AG24" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH24" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI24" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ24" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="C25" s="2"/>
-      <c r="D25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E25" s="2"/>
-      <c r="F25" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K25" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="L25" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
-      <c r="P25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q25" s="2"/>
-      <c r="R25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="Z25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="AG25" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ25" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="C26" s="2"/>
-      <c r="D26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E26" s="2"/>
-      <c r="F26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G26" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="L26" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
-      <c r="P26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q26" s="2"/>
-      <c r="R26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="AG26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH26" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ26" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="C27" s="2"/>
-      <c r="D27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E27" s="2"/>
-      <c r="F27" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G27" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K27" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="L27" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
-      <c r="P27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q27" s="2"/>
-      <c r="R27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AG27" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH27" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ27" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="C28" s="2"/>
-      <c r="D28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E28" s="2"/>
-      <c r="F28" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G28" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K28" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="L28" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
-      <c r="P28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q28" s="2"/>
-      <c r="R28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="AG28" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH28" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ28" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="C29" s="2"/>
-      <c r="D29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E29" s="2"/>
-      <c r="F29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G29" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K29" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="L29" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
-      <c r="P29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q29" s="2"/>
-      <c r="R29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="AG29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH29" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ29" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="C30" s="2"/>
-      <c r="D30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E30" s="2"/>
-      <c r="F30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K30" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="L30" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
-      <c r="P30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q30" s="2"/>
-      <c r="R30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="Z30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AG30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ30" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="C31" s="2"/>
-      <c r="D31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E31" s="2"/>
-      <c r="F31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G31" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K31" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="L31" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
-      <c r="P31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q31" s="2"/>
-      <c r="R31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="AG31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH31" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ31" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="C32" s="2"/>
-      <c r="D32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E32" s="2"/>
-      <c r="F32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G32" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K32" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="L32" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
-      <c r="P32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q32" s="2"/>
-      <c r="R32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="AG32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH32" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ32" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="C33" s="2"/>
-      <c r="D33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E33" s="2"/>
-      <c r="F33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G33" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K33" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="L33" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
-      <c r="P33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q33" s="2"/>
-      <c r="R33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="AG33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH33" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ33" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="C34" s="2"/>
-      <c r="D34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E34" s="2"/>
-      <c r="F34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K34" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="L34" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
-      <c r="P34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q34" s="2"/>
-      <c r="R34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="AG34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ34" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="C35" s="2"/>
-      <c r="D35" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E35" s="2"/>
-      <c r="F35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G35" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H35" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I35" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J35" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="L35" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
-      <c r="P35" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q35" s="2"/>
-      <c r="R35" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S35" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T35" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U35" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V35" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W35" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X35" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z35" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="AG35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH35" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI35" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ35" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="C36" s="2"/>
-      <c r="D36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E36" s="2"/>
-      <c r="F36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G36" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K36" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="L36" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
-      <c r="P36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q36" s="2"/>
-      <c r="R36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF36" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="AG36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH36" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ36" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="B37" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="C37" s="2"/>
-      <c r="D37" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E37" s="2"/>
-      <c r="F37" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G37" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H37" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I37" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J37" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K37" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="L37" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
-      <c r="P37" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q37" s="2"/>
-      <c r="R37" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S37" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T37" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U37" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V37" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W37" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X37" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y37" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z37" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA37" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="AG37" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH37" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI37" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ37" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="B38" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="C38" s="2"/>
-      <c r="D38" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E38" s="2"/>
-      <c r="F38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G38" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H38" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I38" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J38" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K38" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="L38" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
-      <c r="P38" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q38" s="2"/>
-      <c r="R38" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S38" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T38" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U38" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V38" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W38" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X38" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y38" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="Z38" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA38" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AG38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH38" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI38" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ38" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="B39" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="C39" s="2"/>
-      <c r="D39" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E39" s="2"/>
-      <c r="F39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G39" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H39" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I39" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J39" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K39" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="L39" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
-      <c r="P39" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q39" s="2"/>
-      <c r="R39" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S39" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T39" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U39" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V39" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W39" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X39" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z39" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA39" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE39" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF39" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="AG39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH39" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI39" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ39" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/main/ig/StructureDefinition-fr-lm-specimen.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:15:23+00:00</t>
+    <t>2026-08-11T08:03:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-specimen.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T08:03:55+00:00</t>
+    <t>2026-08-11T09:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-specimen.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T09:29:09+00:00</t>
+    <t>2026-08-13T09:45:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-specimen.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:45:33+00:00</t>
+    <t>2026-08-13T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-specimen.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T14:36:19+00:00</t>
+    <t>2026-08-14T12:00:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-specimen.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:00:06+00:00</t>
+    <t>2026-08-14T14:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-specimen.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-specimen.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="144">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T14:57:39+00:00</t>
+    <t>2026-08-20T08:45:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -273,6 +273,9 @@
     <t>Disponibilité du prélèvement</t>
   </si>
   <si>
+    <t>preferred</t>
+  </si>
+  <si>
     <t>(preferred): HL7 specimen-status</t>
   </si>
   <si>
@@ -280,6 +283,9 @@
   </si>
   <si>
     <t>Échantillon prélevé</t>
+  </si>
+  <si>
+    <t>required</t>
   </si>
   <si>
     <t>jdv-specimen-type-cisis (1.2.250.1.213.1.1.5.819)</t>
@@ -1167,10 +1173,10 @@
         <v>73</v>
       </c>
       <c r="X4" t="s" s="2">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="Y4" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Z4" t="s" s="2">
         <v>73</v>
@@ -1208,10 +1214,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1237,10 +1243,10 @@
         <v>83</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1267,13 +1273,13 @@
         <v>73</v>
       </c>
       <c r="X5" t="s" s="2">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="Y5" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="Z5" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AA5" t="s" s="2">
         <v>73</v>
@@ -1291,7 +1297,7 @@
         <v>73</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>74</v>
@@ -1308,10 +1314,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1334,13 +1340,13 @@
         <v>73</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1391,7 +1397,7 @@
         <v>73</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>74</v>
@@ -1408,10 +1414,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1434,13 +1440,13 @@
         <v>73</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1491,7 +1497,7 @@
         <v>73</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>74</v>
@@ -1508,10 +1514,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1534,13 +1540,13 @@
         <v>73</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1591,7 +1597,7 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>74</v>
@@ -1608,10 +1614,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1637,10 +1643,10 @@
         <v>83</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1667,31 +1673,31 @@
         <v>73</v>
       </c>
       <c r="X9" t="s" s="2">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="Y9" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="Z9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF9" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="Z9" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA9" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB9" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD9" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE9" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF9" t="s" s="2">
-        <v>99</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
@@ -1708,10 +1714,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1734,13 +1740,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1791,7 +1797,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -1808,10 +1814,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1834,13 +1840,13 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1891,7 +1897,7 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
@@ -1908,10 +1914,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1934,13 +1940,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -1991,7 +1997,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -2008,10 +2014,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2034,13 +2040,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2091,7 +2097,7 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
@@ -2108,10 +2114,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2137,10 +2143,10 @@
         <v>83</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2167,31 +2173,31 @@
         <v>73</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="Y14" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="Z14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF14" t="s" s="2">
         <v>116</v>
-      </c>
-      <c r="Z14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
@@ -2208,10 +2214,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2234,13 +2240,13 @@
         <v>73</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2291,7 +2297,7 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
@@ -2308,10 +2314,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2334,13 +2340,13 @@
         <v>73</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2391,7 +2397,7 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>74</v>
@@ -2408,10 +2414,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2434,13 +2440,13 @@
         <v>73</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2491,7 +2497,7 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>74</v>
@@ -2508,10 +2514,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2534,13 +2540,13 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2591,7 +2597,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -2608,10 +2614,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2634,13 +2640,13 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2691,7 +2697,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -2708,10 +2714,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2734,13 +2740,13 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2791,7 +2797,7 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>74</v>
@@ -2808,10 +2814,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2834,13 +2840,13 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -2891,7 +2897,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -2908,10 +2914,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -2937,10 +2943,10 @@
         <v>83</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -2967,31 +2973,31 @@
         <v>73</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="Y22" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF22" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="Z22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>136</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
@@ -3008,10 +3014,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3034,13 +3040,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3091,7 +3097,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
